--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,31 @@
         </is>
       </c>
       <c r="E2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fdggd</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rgdtf</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>fdg</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>sfr</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>1</v>
       </c>
     </row>

--- a/results.xlsx
+++ b/results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,31 @@
         </is>
       </c>
       <c r="E3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>9032046252</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>omonikpaparao@gmail.com</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>1</v>
       </c>
     </row>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,6 +528,31 @@
       </c>
       <c r="E4" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sasi</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dhar</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>9989807311</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>sas@gmail.com</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,6 +553,31 @@
       </c>
       <c r="E5" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yaswanth </t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Vardhan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>9505989959</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>yaswanthvardhan216@gmail.com</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,6 +577,31 @@
         </is>
       </c>
       <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yaswanth </t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Vardhan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>9505989959</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>yaswanthvardhan216@gmail.com</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>1</v>
       </c>
     </row>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,6 +605,31 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pradeep</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kumar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7981133094</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>durgaramasatya90@gmail.com</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -630,6 +630,31 @@
         <v>1</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Hdhx</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Xhxh</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>999999999</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Hshsh</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,6 +655,31 @@
         <v>1</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ompr </t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ombr</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>9999998855</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Abcd@gmail.com</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,6 +680,31 @@
         <v>3</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hello</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>46799975</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>W@gmail.com</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,6 +705,31 @@
         <v>1</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Hello</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Venu</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>90321047</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>123@gmail.com</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -730,6 +730,31 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Hello</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Venu</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>90321047</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>123@gmail.com</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -755,6 +755,31 @@
         <v>4</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Spk</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Spk</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>8309179509</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>prasannasimha5002@gmail.com</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,6 +780,31 @@
         <v>1</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>9999999999</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>p@gmail.com</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,6 +805,31 @@
         <v>5</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>z</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>z</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>9999999999</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>zz</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -830,6 +830,31 @@
         <v>1</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>eq</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>swww</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ww</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>swwz</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -855,6 +855,31 @@
         <v>1</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Pra</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Kungfu</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -880,6 +880,31 @@
         <v>1</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Lavada</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Benchuth</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>8262829928</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>erripuku@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,6 +905,31 @@
         <v>5</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ganesh</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>gg</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>54156</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>656556</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -930,6 +930,31 @@
         <v>2</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Mani</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tej</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>6302590086</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>manitejakukatla2023@outlook.com</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -955,6 +955,31 @@
         <v>8</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Lavada</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Benchuth</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>8262829928</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>erripuku@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,6 +980,31 @@
         <v>6</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Gkkhg</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Gkkg</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>46789</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>abc@gmail.com</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1005,6 +1005,31 @@
         <v>5</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>vitesh</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>babu</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>8639811361</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>viteshbabukatlai03023@gmail.com</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,6 +1030,31 @@
         <v>4</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ajay23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>balaji</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>07386467667</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>pardhumannem7@outlook.com</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1055,6 +1055,31 @@
         <v>6</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Pra</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Kungfu</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,6 +1080,31 @@
         <v>8</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Hii</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Hello</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Abc@gmail.com</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1105,6 +1105,31 @@
         <v>7</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yaswanth </t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Vardhan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>9505989959</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>yaswanthvardhan216@gmail.com</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1130,6 +1130,31 @@
         <v>3</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sasidhar</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Mech</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0987654321</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>sas@gmail.com</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1155,6 +1155,31 @@
         <v>5</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KOTAPATI GOPI KRISHNA </t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KRISHNA </t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>7207194616</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>allluvijay23@gmail.com</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1180,6 +1180,31 @@
         <v>3</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dhanush </t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dhanush </t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>9949090501</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>dhanushkaka02@gmail.com</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1205,6 +1205,31 @@
         <v>6</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Pardhu</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>9090908080</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PAhh@gmail.com</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1230,6 +1230,31 @@
         <v>3</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Kukkapalli maniteja</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kukatla nagasai</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Aa@gmail.com</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,6 +1255,31 @@
         <v>1</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Nagasai</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Alsaba</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>888888888</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Nagaalsu@gmail.com</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1280,6 +1280,31 @@
         <v>1</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sai</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>sudheer</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>6300322074</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>saisudheer.1842@gmail.com</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,8 @@
           <t>y22cs145</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>9032046252</t>
-        </is>
+      <c r="E2" t="n">
+        <v>9032046252</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -498,6 +496,41 @@
       </c>
       <c r="G2" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hkj</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>hjbk</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>y22cs145</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>y22cs180</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>yvjl</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>bjnkm</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,6 +530,41 @@
         </is>
       </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hello</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>welcome</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Y22C009</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Y22CS00</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>gyhu</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>1</v>
       </c>
     </row>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,6 +565,41 @@
         </is>
       </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>m,.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>nm, .</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>M, .</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>M, .</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>m, .</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>,m .</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>1</v>
       </c>
     </row>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,6 +601,41 @@
       </c>
       <c r="G5" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hjklm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>nm</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NM,</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NM,.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>,m.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>jklm</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,6 +636,41 @@
       </c>
       <c r="G6" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>fsgdf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sfdg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FGN</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DFGH</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>wsdfg</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>er</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,6 +671,41 @@
       </c>
       <c r="G7" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ompr</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>OMPR</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>KLM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>KLM;</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -708,6 +708,41 @@
         <v>9</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>65676</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>45678</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,6 +743,41 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sai</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sai1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HJB</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BNJ</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>hbmn</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nm, </t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,33 @@
         <v>1</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>233r55577</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>123456788</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,6 +805,33 @@
         <v>3</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Gzh</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Jjejsj</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sjjs</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ndjs</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -832,6 +832,41 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>omonik</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>paparao</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>9032046252</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>123@gmail.com</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -867,6 +867,41 @@
         <v>3</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Y22cs139</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nnj</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>35GG</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TU8</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>6864369876</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>123@gmail</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,6 +902,41 @@
         <v>0</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Monik</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pavan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Y22CS139</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Y22CS184</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>6302004943</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>omonikpaparao@gmail.com</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -937,6 +937,41 @@
         <v>1</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Pendyala Skanda Bhagavan</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>OMPR</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Y22</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Y32</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8973947988</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>123@gmail.com</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -972,6 +972,41 @@
         <v>1</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sasi Vardhan</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>harsha</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Y22CS191</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Y22CS155</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>y22cs139@rvrjc.ac.in</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1007,6 +1007,41 @@
         <v>1</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>paparao</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sruthi</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Y22CS141</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Y22CS138</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>984800121</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ompr@gmail.com</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,41 +413,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Participant 1</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Participant 2</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Roll-1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Roll-2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
@@ -1039,6 +1027,41 @@
         </is>
       </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Hhh</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ttt</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bhb@;;!.com</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/results.xlsx
+++ b/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1065,6 +1065,41 @@
         <v>0</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Yge</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ywhhw</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GHEH</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>5WGGW</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Yh@ghh.clmm</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1100,6 +1100,41 @@
         <v>0</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>dhanu swetha</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>devarasetti</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0987654321</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>dhanuswethadevarasetti@gmail.com</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1135,6 +1135,41 @@
         <v>11</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DWEDD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>WEF</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>324532</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>vghjb@hgvjb.com</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1170,6 +1170,41 @@
         <v>0</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>gowthami</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>lakshmi</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>9854712365</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>gowthamilakshmi1997@gmail.com</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1205,6 +1205,41 @@
         <v>11</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ksdq</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>klnmd</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>KJNKMDSF</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LHDEIUHN</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>88289378</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ewdkjn@yljkmds.com</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1240,6 +1240,41 @@
         <v>14</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>iuhjbk</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>kjfe</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>KJLKEF</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ILUHJMK</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>893803009</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>jbhnw@khbnj.com</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1275,6 +1275,41 @@
         <v>0</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Himaja</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Himaja</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Y22CSCM982</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Y22CSCM982</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>9861475536</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>himaja@gmail.com</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1310,6 +1310,41 @@
         <v>15</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sharanya</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>sharanya</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Y22CSCM348</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Y22CSCM348</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2315786565</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>99250040014@klu.ac.in</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1345,6 +1345,41 @@
         <v>15</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>venkata umesh</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>venkata umesh</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Y22CSCM9560</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Y22CSCM9560</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>9866950702</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>venkat@gmail.com</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1380,6 +1380,41 @@
         <v>10</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Hello</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>hasdjo</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Y89</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>7IJK</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>123@hjsk.com</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1415,6 +1415,41 @@
         <v>0</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gowthami </t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gowthami </t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>9701583098</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>gowthamilakshmi208@gmail.com</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1450,6 +1450,41 @@
         <v>46</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Dhanu swetha</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Devarasetti</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0987654321</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>dhanuswethadevarasetti@gmail.com</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results.xlsx
+++ b/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1485,6 +1485,41 @@
         <v>46</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>GANESH</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yalamanchili </t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>27/08/2007</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>27/08/2008</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0136794594</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>yalamanchiligeethakrishna2@gmail.com</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
